--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -594,11 +594,17 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>41233</v>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>справочник Ozon</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -780,7 +786,7 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -814,7 +820,7 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -848,7 +854,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1086,11 +1092,17 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>41233</v>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>справочник Ozon</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1276,7 +1288,7 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1310,7 +1322,7 @@
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1344,7 +1356,7 @@
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="План" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,14 +526,22 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
+          <t>владелец: комплект из 4 × 0AM325413A</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -607,7 +615,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -636,16 +648,20 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок — 4 шт.</t>
+          <t>Сальник толкателя вилки 0AM325413A — 4 шт.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>из названия — проверьте</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>владелец: 4 × 0AM325413A</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -683,7 +699,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -986,14 +1006,22 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
+          <t>maktrans.net: 24.3×13.5×8.7 мм</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1028,10 +1056,14 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>артикул из названия</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+          <t>артикул</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1105,7 +1137,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1134,16 +1170,20 @@
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки — 1 шт.</t>
+          <t>Сальник толкателя вилки 0AM325413A — 1 шт.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>из названия — проверьте</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>проверено владельцем</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1181,7 +1221,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1488,14 +1532,22 @@
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr"/>
+          <t>maktrans.net: 24.3×13.5×8.7 мм</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="План" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -504,12 +504,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -526,32 +526,28 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>0AM325413A</t>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>владелец: комплект из 4 × 0AM325413A</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>артикул из названия</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -580,12 +576,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -615,21 +611,17 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -648,30 +640,26 @@
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки 0AM325413A — 4 шт.</t>
+          <t>Фильтр — 1 шт.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>владелец: 4 × 0AM325413A</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -690,30 +678,26 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>из названия</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -746,12 +730,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -767,12 +751,16 @@
           <t>String</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>#фильтр_02e305051c #02e305051c_фильтр_масляный</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>нужны данные от вас</t>
+          <t>уже заполнено — не трогаем</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -780,12 +768,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -814,12 +802,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -848,12 +836,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -882,12 +870,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -916,12 +904,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -950,12 +938,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -984,12 +972,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Фильтр мехатроника DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1006,32 +994,24 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>maktrans.net: 24.3×13.5×8.7 мм</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1050,30 +1030,26 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>артикул</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>артикул из названия</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1102,12 +1078,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1137,21 +1113,17 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="J18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1170,30 +1142,26 @@
       <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки 0AM325413A — 1 шт.</t>
+          <t>Транспортная заглушка — 1 шт.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>проверено владельцем</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1221,21 +1189,17 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="J20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1268,12 +1232,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1291,7 +1255,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>#сальники_толкателей_дсг_7 #сальники_толкателей_dq200 #сальники_толкателей_вилок</t>
+          <t>#заглушка_dq200 #заглушка_дсг_7 #заглушка_кпп_dq200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1306,12 +1270,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1340,12 +1304,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1374,12 +1338,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1408,12 +1372,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1442,12 +1406,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1476,12 +1440,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1510,12 +1474,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1532,22 +1496,3854 @@
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>maktrans.net: 24.3×13.5×8.7 мм</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>0AM325477AE</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>артикул из названия</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов — 1 шт.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>#соленоид_регулятор_давления #регулятор_давления</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>0AM325477</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>артикул из названия</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Планка соленоидов — 1 шт.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>#планка #соленоид #мехатроник #dsg7 #dq200 #0am #0cw</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW, пластик, 1 шт</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Сальники штоков — 2 шт.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>из названия</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, — 2 шт.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>из названия</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, — 1 шт.</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Прокладка крышки — 1 шт.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>#прокладка_крышки_dq200 #прокладка_поддона_dq200 #dq200 #dsg7 #мехатроник</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr"/>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr"/>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока — 1 шт.</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr"/>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Количество в упаковке, шт</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>8513</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Количество, штук</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>справочник</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr"/>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>#Прокладкаdq200</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>уже заполнено — не трогаем</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr"/>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Цвет товара</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>10096</v>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Расположение детали</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>20189</v>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr"/>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>выберите: Слева [971010416]; Справа [971010417]; Спереди [971010418]; Сзади [971010419]</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr"/>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>9799</v>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr"/>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний диаметр, мм</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>7368</v>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr"/>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>OEM-номер</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Альтернативные артикулы товара</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>11031</v>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>0B5325421</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr"/>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>другие коды из названия/описания</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Вид техники</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Легковые автомобили</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>41233</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>справочник Ozon</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Комплектация</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>4384</v>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды — 1 шт.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>из названия — проверьте</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Единиц в одном товаре</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>8962</v>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>одна деталь</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>#Хештеги</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>23171</v>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>7199</v>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>справочник (список)</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Длина, мм</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>9802</v>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Ширина, мм</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>6605</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Decimal</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Высота, мм</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>нужны данные от вас</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="План" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -537,7 +537,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -611,7 +615,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -649,7 +657,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -687,7 +699,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1039,7 +1055,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1113,7 +1133,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1151,7 +1175,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1189,7 +1217,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1541,7 +1573,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1615,7 +1651,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1653,7 +1693,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1691,7 +1735,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1729,7 +1777,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2117,7 +2169,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2155,7 +2211,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2193,7 +2253,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2231,7 +2295,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2615,7 +2683,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2644,7 +2716,7 @@
       <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Сальники штоков — 2 шт.</t>
+          <t>Сальник штока — 2 шт.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -2653,7 +2725,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2691,7 +2767,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3109,7 +3189,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3138,7 +3222,7 @@
       <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, — 2 шт.</t>
+          <t>Сальник штока оригинальный VAG — 2 шт.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -3147,7 +3231,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3185,7 +3273,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3603,7 +3695,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3632,7 +3728,7 @@
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, — 1 шт.</t>
+          <t>Сальник штока оригинальный VAG — 1 шт.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr"/>
@@ -3641,7 +3737,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3679,7 +3779,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4097,7 +4201,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4135,7 +4243,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4173,7 +4285,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4595,7 +4711,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4633,7 +4753,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4671,7 +4795,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4709,7 +4837,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -5057,7 +5189,11 @@
           <t>другие коды из названия/описания</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5097,7 +5233,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5126,7 +5266,7 @@
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>Оригинальная фильтр-сетка на соленоиды — 1 шт.</t>
+          <t>Фильтр-сетка на соленоиды оригинальная — 1 шт.</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
@@ -5135,7 +5275,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5173,7 +5317,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1812,14 +1812,22 @@
           <t>#соленоид_регулятор_давления #регулятор_давления</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>#пластина_соленоидов_dq200 #0am325477ae #мехатроник_dq200</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
           <t>уже заполнено — не трогаем</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>заменить</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2171,7 +2179,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2221,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2263,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2305,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2693,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2735,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2777,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3199,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3241,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3283,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3705,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3747,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3789,7 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4211,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4253,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4295,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4721,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4763,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4797,7 +4805,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4847,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5199,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5243,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5285,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5327,7 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="План" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -537,7 +537,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -611,7 +615,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -649,7 +657,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -687,7 +699,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1039,7 +1055,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1077,7 +1097,11 @@
           <t>другие коды из названия/описания</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1117,7 +1141,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1533,7 +1561,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1607,7 +1639,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1645,7 +1681,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1683,7 +1723,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1969,7 +2013,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2045,7 +2093,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2257,7 +2309,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2295,7 +2351,11 @@
           <t>другие коды из названия/описания</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2335,7 +2395,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2364,7 +2428,7 @@
       <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>Алюминиевый корпус масляного фильтра EA888 Gen3 (крышка, колба, корпус обратного клапана) 06L115401S для 1.8 2.0 TSI — 1 шт.</t>
+          <t>Корпус масляного фильтра в сборе (крышка, колба, корпус обратного клапана) — 1 шт.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -2373,7 +2437,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2697,7 +2765,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2773,7 +2845,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3059,7 +3135,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3549,7 +3629,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3587,7 +3671,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3625,7 +3713,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3663,7 +3755,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4047,7 +4143,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4085,7 +4185,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4123,7 +4227,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4541,7 +4649,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4579,7 +4691,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4617,7 +4733,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -5035,7 +5155,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5064,7 +5188,7 @@
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, — 2 шт.</t>
+          <t>Пыльник штока оригинальный VAG — 2 шт.</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
@@ -5073,7 +5197,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5111,7 +5239,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5529,7 +5661,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5558,7 +5694,7 @@
       <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, — 1 шт.</t>
+          <t>Сальник штока оригинальный VAG — 1 шт.</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr"/>
@@ -5567,7 +5703,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5605,7 +5745,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5953,7 +6097,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -6027,7 +6175,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6065,7 +6217,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6103,7 +6259,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6525,7 +6685,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -7011,7 +7175,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -7497,7 +7665,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -7535,7 +7707,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J199" s="2" t="inlineStr"/>
+      <c r="J199" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7919,7 +8095,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J210" s="2" t="inlineStr"/>
+      <c r="J210" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -7957,7 +8137,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J211" s="2" t="inlineStr"/>
+      <c r="J211" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -7995,7 +8179,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J212" s="2" t="inlineStr"/>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8413,7 +8601,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J224" s="2" t="inlineStr"/>
+      <c r="J224" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -8451,7 +8643,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J225" s="2" t="inlineStr"/>
+      <c r="J225" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8489,7 +8685,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -8527,7 +8727,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J227" s="2" t="inlineStr"/>
+      <c r="J227" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -8907,7 +9111,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J238" s="2" t="inlineStr"/>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -8945,7 +9153,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J239" s="2" t="inlineStr"/>
+      <c r="J239" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -8983,7 +9195,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J240" s="2" t="inlineStr"/>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -9320,14 +9536,22 @@
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr"/>
-      <c r="G250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>55565480</t>
+        </is>
+      </c>
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="2" t="inlineStr">
         <is>
           <t>нужны данные от вас</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr"/>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -9354,14 +9578,22 @@
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr"/>
-      <c r="G251" s="2" t="inlineStr"/>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>5636119</t>
+        </is>
+      </c>
       <c r="H251" s="2" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr">
         <is>
           <t>нужны данные от вас</t>
         </is>
       </c>
-      <c r="J251" s="2" t="inlineStr"/>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -9401,7 +9633,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr"/>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -9430,7 +9666,7 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119) — 1 шт.</t>
+          <t>Импульсное кольцо распредвала — 1 шт.</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
@@ -9439,7 +9675,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J253" s="2" t="inlineStr"/>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -9849,7 +10089,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J264" s="2" t="inlineStr"/>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -9935,7 +10179,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J266" s="2" t="inlineStr"/>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -9973,7 +10221,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J267" s="2" t="inlineStr"/>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -10011,7 +10263,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -10461,7 +10717,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J280" s="2" t="inlineStr"/>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -10975,7 +11235,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J294" s="2" t="inlineStr"/>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -11489,7 +11753,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J308" s="2" t="inlineStr"/>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -11921,7 +12189,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J320" s="2" t="inlineStr"/>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -11995,7 +12267,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J322" s="2" t="inlineStr"/>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -12349,7 +12625,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J332" s="2" t="inlineStr"/>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -12378,7 +12658,7 @@
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>Оригинальные пластины на соленоиды VAG — 1 шт.</t>
+          <t>Пластина на соленоиды оригинальная VAG — 2 шт.</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr"/>
@@ -12387,7 +12667,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J333" s="2" t="inlineStr"/>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -12416,7 +12700,7 @@
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr"/>
@@ -12425,7 +12709,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J334" s="2" t="inlineStr"/>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -12847,7 +13135,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J346" s="2" t="inlineStr"/>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -12876,7 +13168,7 @@
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK — 4 шт.</t>
+          <t>Подшипник вариатора JF011E — 4 шт.</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr"/>
@@ -12885,7 +13177,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J347" s="2" t="inlineStr"/>
+      <c r="J347" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -13285,7 +13581,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J358" s="2" t="inlineStr"/>
+      <c r="J358" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -13799,7 +14099,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J372" s="2" t="inlineStr"/>
+      <c r="J372" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -14231,7 +14535,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J384" s="2" t="inlineStr"/>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -14305,7 +14613,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J386" s="2" t="inlineStr"/>
+      <c r="J386" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -14381,7 +14693,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J388" s="2" t="inlineStr"/>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -14663,7 +14979,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J396" s="2" t="inlineStr"/>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -14701,7 +15021,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J397" s="2" t="inlineStr"/>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -14739,7 +15063,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J398" s="2" t="inlineStr"/>
+      <c r="J398" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -15185,7 +15513,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J410" s="2" t="inlineStr"/>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -15687,7 +16019,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J424" s="2" t="inlineStr"/>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -15725,7 +16061,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J425" s="2" t="inlineStr"/>
+      <c r="J425" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -15763,7 +16103,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J426" s="2" t="inlineStr"/>
+      <c r="J426" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -16213,7 +16557,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J438" s="2" t="inlineStr"/>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -16251,7 +16599,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J439" s="2" t="inlineStr"/>
+      <c r="J439" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -16289,7 +16641,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J440" s="2" t="inlineStr"/>
+      <c r="J440" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -16735,7 +17091,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J452" s="2" t="inlineStr"/>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -17249,7 +17609,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J466" s="2" t="inlineStr"/>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -17767,7 +18131,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J480" s="2" t="inlineStr"/>
+      <c r="J480" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -18273,7 +18641,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J494" s="2" t="inlineStr"/>
+      <c r="J494" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -5157,7 +5157,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5199,7 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="J320" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J347" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -10091,7 +10091,7 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11755,7 @@
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="J320" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="J322" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12711,7 +12711,7 @@
       </c>
       <c r="J334" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J347" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="J358" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="J372" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="J386" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18133,7 @@
       </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -14981,7 +14981,7 @@
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15023,7 +15023,7 @@
       </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
       </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="J425" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="J426" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="J439" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16643,7 +16643,7 @@
       </c>
       <c r="J440" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17611,7 +17611,7 @@
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18133,7 @@
       </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="План" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="План" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -649,7 +653,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -687,7 +695,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -725,7 +737,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1039,7 +1055,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1117,7 +1137,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1627,7 +1651,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1665,7 +1693,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1703,7 +1735,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1741,7 +1777,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2055,7 +2095,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2133,7 +2177,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2171,7 +2219,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2209,7 +2261,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2247,7 +2303,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2561,7 +2621,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2639,7 +2703,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2677,7 +2745,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2715,7 +2787,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3157,7 +3233,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3195,7 +3275,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3233,7 +3317,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3271,7 +3359,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3655,7 +3747,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4079,7 +4175,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4153,7 +4253,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4191,7 +4295,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4229,7 +4337,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4581,7 +4693,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4655,7 +4771,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4693,7 +4813,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4731,7 +4855,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5083,7 +5211,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5161,7 +5293,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5593,7 +5729,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5667,7 +5807,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -6087,7 +6231,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6161,7 +6309,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6667,7 +6819,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -6705,7 +6861,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -6743,7 +6903,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -7111,7 +7275,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -7185,7 +7353,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -7223,7 +7395,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -7261,7 +7437,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -7609,7 +7789,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J198" s="2" t="inlineStr"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -7683,7 +7867,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J200" s="2" t="inlineStr"/>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -7721,7 +7909,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J201" s="2" t="inlineStr"/>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -7759,7 +7951,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J202" s="2" t="inlineStr"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -8189,7 +8385,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -8227,7 +8427,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -8265,7 +8469,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -8633,7 +8841,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J226" s="2" t="inlineStr"/>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -8707,7 +8919,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J228" s="2" t="inlineStr"/>
+      <c r="J228" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -8745,7 +8961,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J229" s="2" t="inlineStr"/>
+      <c r="J229" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8783,7 +9003,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J230" s="2" t="inlineStr"/>
+      <c r="J230" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -9209,7 +9433,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J242" s="2" t="inlineStr"/>
+      <c r="J242" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -9703,7 +9931,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J256" s="2" t="inlineStr"/>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -9732,7 +9964,7 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков — 2 шт.</t>
+          <t>Ремкомплект для 2 штоков — 1 компл.</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr"/>
@@ -9741,7 +9973,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J257" s="2" t="inlineStr"/>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -10131,7 +10367,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J268" s="2" t="inlineStr"/>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -10209,7 +10449,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J270" s="2" t="inlineStr"/>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -10247,7 +10491,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J271" s="2" t="inlineStr"/>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -10285,7 +10533,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J272" s="2" t="inlineStr"/>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -10649,7 +10901,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J282" s="2" t="inlineStr"/>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -10723,7 +10979,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J284" s="2" t="inlineStr"/>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -11237,7 +11497,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J298" s="2" t="inlineStr"/>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -11275,7 +11539,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J299" s="2" t="inlineStr"/>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -11313,7 +11581,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J300" s="2" t="inlineStr"/>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -11677,7 +11949,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J310" s="2" t="inlineStr"/>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -11751,7 +12027,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J312" s="2" t="inlineStr"/>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -11789,7 +12069,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J313" s="2" t="inlineStr"/>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -11827,7 +12111,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J314" s="2" t="inlineStr"/>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -12179,7 +12467,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J324" s="2" t="inlineStr"/>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -12253,7 +12545,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J326" s="2" t="inlineStr"/>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -12673,7 +12969,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J338" s="2" t="inlineStr"/>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -12751,7 +13051,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J340" s="2" t="inlineStr"/>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -12789,7 +13093,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J341" s="2" t="inlineStr"/>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -12827,7 +13135,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J342" s="2" t="inlineStr"/>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -12865,7 +13177,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J343" s="2" t="inlineStr"/>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -13257,7 +13573,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J354" s="2" t="inlineStr"/>
+      <c r="J354" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -13751,7 +14071,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J368" s="2" t="inlineStr"/>
+      <c r="J368" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -14237,7 +14561,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J382" s="2" t="inlineStr"/>
+      <c r="J382" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -14266,7 +14594,7 @@
       <c r="F383" s="2" t="inlineStr"/>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>Оригинальный пыльник штока — 1 шт.</t>
+          <t>Пыльник штока оригинальный — 1 шт.</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr"/>
@@ -14275,7 +14603,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J383" s="2" t="inlineStr"/>
+      <c r="J383" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -14313,7 +14645,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J384" s="2" t="inlineStr"/>
+      <c r="J384" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -14351,7 +14687,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J385" s="2" t="inlineStr"/>
+      <c r="J385" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -14735,7 +15075,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J396" s="2" t="inlineStr"/>
+      <c r="J396" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -14773,7 +15117,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J397" s="2" t="inlineStr"/>
+      <c r="J397" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -15087,7 +15435,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J406" s="2" t="inlineStr"/>
+      <c r="J406" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -15161,7 +15513,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J408" s="2" t="inlineStr"/>
+      <c r="J408" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -15199,7 +15555,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J409" s="2" t="inlineStr"/>
+      <c r="J409" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -15237,7 +15597,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J410" s="2" t="inlineStr"/>
+      <c r="J410" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -15589,7 +15953,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J420" s="2" t="inlineStr"/>
+      <c r="J420" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -15663,7 +16031,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J422" s="2" t="inlineStr"/>
+      <c r="J422" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -15701,7 +16073,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J423" s="2" t="inlineStr"/>
+      <c r="J423" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -15739,7 +16115,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J424" s="2" t="inlineStr"/>
+      <c r="J424" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -16091,7 +16471,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J434" s="2" t="inlineStr"/>
+      <c r="J434" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -16169,7 +16553,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J436" s="2" t="inlineStr"/>
+      <c r="J436" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -16207,7 +16595,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J437" s="2" t="inlineStr"/>
+      <c r="J437" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -16245,7 +16637,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J438" s="2" t="inlineStr"/>
+      <c r="J438" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -16613,7 +17009,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J448" s="2" t="inlineStr"/>
+      <c r="J448" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -16687,7 +17087,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J450" s="2" t="inlineStr"/>
+      <c r="J450" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -16763,7 +17167,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J452" s="2" t="inlineStr"/>
+      <c r="J452" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -17205,7 +17613,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J464" s="2" t="inlineStr"/>
+      <c r="J464" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -17234,7 +17646,7 @@
       <c r="F465" s="2" t="inlineStr"/>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, — 2 шт.</t>
+          <t>Пыльник штока оригинальный VAG — 2 шт.</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr"/>
@@ -17243,7 +17655,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J465" s="2" t="inlineStr"/>
+      <c r="J465" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -17281,7 +17697,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J466" s="2" t="inlineStr"/>
+      <c r="J466" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -17629,7 +18049,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J476" s="2" t="inlineStr"/>
+      <c r="J476" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -17703,7 +18127,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J478" s="2" t="inlineStr"/>
+      <c r="J478" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -17741,7 +18169,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J479" s="2" t="inlineStr"/>
+      <c r="J479" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -17779,7 +18211,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J480" s="2" t="inlineStr"/>
+      <c r="J480" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -18131,7 +18567,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J490" s="2" t="inlineStr"/>
+      <c r="J490" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -18205,7 +18645,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J492" s="2" t="inlineStr"/>
+      <c r="J492" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -18234,7 +18678,7 @@
       <c r="F493" s="2" t="inlineStr"/>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>Обратный клапан масляного фильтра EA888 Gen3 06L115678AD для двигателей 1.8 2.0 TSI — 1 шт.</t>
+          <t>Обратный клапан масляного фильтра — 1 шт.</t>
         </is>
       </c>
       <c r="H493" s="2" t="inlineStr"/>
@@ -18243,7 +18687,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J493" s="2" t="inlineStr"/>
+      <c r="J493" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -18281,7 +18729,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J494" s="2" t="inlineStr"/>
+      <c r="J494" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -18567,7 +19019,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J502" s="2" t="inlineStr"/>
+      <c r="J502" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -18605,7 +19061,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J503" s="2" t="inlineStr"/>
+      <c r="J503" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -18643,7 +19103,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J504" s="2" t="inlineStr"/>
+      <c r="J504" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -19069,7 +19533,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J516" s="2" t="inlineStr"/>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -19485,7 +19953,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J528" s="2" t="inlineStr"/>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -19559,7 +20031,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J530" s="2" t="inlineStr"/>
+      <c r="J530" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -19597,7 +20073,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J531" s="2" t="inlineStr"/>
+      <c r="J531" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -19635,7 +20115,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J532" s="2" t="inlineStr"/>
+      <c r="J532" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
@@ -20065,7 +20549,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J544" s="2" t="inlineStr"/>
+      <c r="J544" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
@@ -20485,7 +20973,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J556" s="2" t="inlineStr"/>
+      <c r="J556" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -20559,7 +21051,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J558" s="2" t="inlineStr"/>
+      <c r="J558" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -20597,7 +21093,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J559" s="2" t="inlineStr"/>
+      <c r="J559" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -20635,7 +21135,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J560" s="2" t="inlineStr"/>
+      <c r="J560" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -20987,7 +21491,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J570" s="2" t="inlineStr"/>
+      <c r="J570" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -21065,7 +21573,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J572" s="2" t="inlineStr"/>
+      <c r="J572" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -21103,7 +21615,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J573" s="2" t="inlineStr"/>
+      <c r="J573" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -21141,7 +21657,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J574" s="2" t="inlineStr"/>
+      <c r="J574" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -21493,7 +22013,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J584" s="2" t="inlineStr"/>
+      <c r="J584" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -21567,7 +22091,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -21605,7 +22133,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J587" s="2" t="inlineStr"/>
+      <c r="J587" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -21643,7 +22175,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J588" s="2" t="inlineStr"/>
+      <c r="J588" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -22065,7 +22601,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J600" s="2" t="inlineStr"/>
+      <c r="J600" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
@@ -22493,7 +23033,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J612" s="2" t="inlineStr"/>
+      <c r="J612" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -22567,7 +23111,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J614" s="2" t="inlineStr"/>
+      <c r="J614" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -22605,7 +23153,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J615" s="2" t="inlineStr"/>
+      <c r="J615" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
@@ -22643,7 +23195,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J616" s="2" t="inlineStr"/>
+      <c r="J616" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
@@ -23061,7 +23617,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J628" s="2" t="inlineStr"/>
+      <c r="J628" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -23099,7 +23659,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J629" s="2" t="inlineStr"/>
+      <c r="J629" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -23137,7 +23701,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J630" s="2" t="inlineStr"/>
+      <c r="J630" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -23175,7 +23743,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J631" s="2" t="inlineStr"/>
+      <c r="J631" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -23559,7 +24131,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J642" s="2" t="inlineStr"/>
+      <c r="J642" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -23597,7 +24173,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J643" s="2" t="inlineStr"/>
+      <c r="J643" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -23635,7 +24215,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J644" s="2" t="inlineStr"/>
+      <c r="J644" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -24057,7 +24641,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J656" s="2" t="inlineStr"/>
+      <c r="J656" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="2" t="inlineStr">
@@ -24086,7 +24674,7 @@
       <c r="F657" s="2" t="inlineStr"/>
       <c r="G657" s="3" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, — 4 шт.</t>
+          <t>Сальник толкателя алюминиевый усиленный — 4 шт.</t>
         </is>
       </c>
       <c r="H657" s="2" t="inlineStr"/>
@@ -24095,7 +24683,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J657" s="2" t="inlineStr"/>
+      <c r="J657" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -24133,7 +24725,11 @@
           <t>из названия</t>
         </is>
       </c>
-      <c r="J658" s="2" t="inlineStr"/>
+      <c r="J658" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
@@ -24559,7 +25155,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J670" s="2" t="inlineStr"/>
+      <c r="J670" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -24597,7 +25197,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J671" s="2" t="inlineStr"/>
+      <c r="J671" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -24635,7 +25239,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J672" s="2" t="inlineStr"/>
+      <c r="J672" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -24917,7 +25525,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J680" s="2" t="inlineStr"/>
+      <c r="J680" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" s="2" t="inlineStr">
@@ -24955,7 +25567,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J681" s="2" t="inlineStr"/>
+      <c r="J681" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -24993,7 +25609,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J682" s="2" t="inlineStr"/>
+      <c r="J682" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -25031,7 +25651,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J683" s="2" t="inlineStr"/>
+      <c r="J683" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -25419,7 +26043,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J694" s="2" t="inlineStr"/>
+      <c r="J694" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -25457,7 +26085,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J695" s="2" t="inlineStr"/>
+      <c r="J695" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -25495,7 +26127,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J696" s="2" t="inlineStr"/>
+      <c r="J696" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -25847,7 +26483,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J706" s="2" t="inlineStr"/>
+      <c r="J706" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -25921,7 +26561,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J708" s="2" t="inlineStr"/>
+      <c r="J708" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -25959,7 +26603,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J709" s="2" t="inlineStr"/>
+      <c r="J709" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -25997,7 +26645,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J710" s="2" t="inlineStr"/>
+      <c r="J710" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" s="2" t="inlineStr">
@@ -26209,7 +26861,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J716" s="2" t="inlineStr"/>
+      <c r="J716" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" s="2" t="inlineStr">
@@ -26283,7 +26939,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J718" s="2" t="inlineStr"/>
+      <c r="J718" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -26321,7 +26981,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J719" s="2" t="inlineStr"/>
+      <c r="J719" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="2" t="inlineStr">
@@ -26359,7 +27023,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J720" s="2" t="inlineStr"/>
+      <c r="J720" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -26727,7 +27395,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J730" s="2" t="inlineStr"/>
+      <c r="J730" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="2" t="inlineStr">
@@ -26801,7 +27473,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J732" s="2" t="inlineStr"/>
+      <c r="J732" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" s="2" t="inlineStr">
@@ -26839,7 +27515,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J733" s="2" t="inlineStr"/>
+      <c r="J733" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="734">
       <c r="A734" s="2" t="inlineStr">
@@ -26877,7 +27557,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J734" s="2" t="inlineStr"/>
+      <c r="J734" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="735">
       <c r="A735" s="2" t="inlineStr">
@@ -27229,7 +27913,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J744" s="2" t="inlineStr"/>
+      <c r="J744" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="745">
       <c r="A745" s="2" t="inlineStr">
@@ -27303,7 +27991,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J746" s="2" t="inlineStr"/>
+      <c r="J746" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" s="2" t="inlineStr">
@@ -27341,7 +28033,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J747" s="2" t="inlineStr"/>
+      <c r="J747" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="748">
       <c r="A748" s="2" t="inlineStr">
@@ -27379,7 +28075,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J748" s="2" t="inlineStr"/>
+      <c r="J748" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="2" t="inlineStr">
@@ -27801,7 +28501,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J760" s="2" t="inlineStr"/>
+      <c r="J760" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" s="2" t="inlineStr">
@@ -27839,7 +28543,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J761" s="2" t="inlineStr"/>
+      <c r="J761" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" s="2" t="inlineStr">
@@ -27877,7 +28585,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J762" s="2" t="inlineStr"/>
+      <c r="J762" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" s="2" t="inlineStr">
@@ -28303,7 +29015,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J774" s="2" t="inlineStr"/>
+      <c r="J774" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" s="2" t="inlineStr">
@@ -28332,7 +29048,7 @@
       <c r="F775" s="2" t="inlineStr"/>
       <c r="G775" s="3" t="inlineStr">
         <is>
-          <t>2 кольца-прокладки на 1 втулку — 1 шт.</t>
+          <t>Кольцо-прокладка втулки штока — 2 шт.</t>
         </is>
       </c>
       <c r="H775" s="2" t="inlineStr"/>
@@ -28341,7 +29057,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J775" s="2" t="inlineStr"/>
+      <c r="J775" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" s="2" t="inlineStr">
@@ -28370,7 +29090,7 @@
       <c r="F776" s="2" t="inlineStr"/>
       <c r="G776" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H776" s="2" t="inlineStr"/>
@@ -28379,7 +29099,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J776" s="2" t="inlineStr"/>
+      <c r="J776" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" s="2" t="inlineStr">
@@ -29817,7 +30541,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J816" s="2" t="inlineStr"/>
+      <c r="J816" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" s="2" t="inlineStr">
@@ -29846,7 +30574,7 @@
       <c r="F817" s="2" t="inlineStr"/>
       <c r="G817" s="3" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C — 1 шт.</t>
+          <t>Гидроблок вариатора — 1 шт.</t>
         </is>
       </c>
       <c r="H817" s="2" t="inlineStr"/>
@@ -29855,7 +30583,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J817" s="2" t="inlineStr"/>
+      <c r="J817" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="818">
       <c r="A818" s="2" t="inlineStr">
@@ -29893,7 +30625,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J818" s="2" t="inlineStr"/>
+      <c r="J818" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" s="2" t="inlineStr">
@@ -29931,7 +30667,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J819" s="2" t="inlineStr"/>
+      <c r="J819" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" s="2" t="inlineStr">
@@ -30311,7 +31051,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J830" s="2" t="inlineStr"/>
+      <c r="J830" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" s="2" t="inlineStr">
@@ -30340,7 +31084,7 @@
       <c r="F831" s="2" t="inlineStr"/>
       <c r="G831" s="3" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C — 1 шт.</t>
+          <t>Гидроблок вариатора — 1 шт.</t>
         </is>
       </c>
       <c r="H831" s="2" t="inlineStr"/>
@@ -30349,7 +31093,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J831" s="2" t="inlineStr"/>
+      <c r="J831" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="832">
       <c r="A832" s="2" t="inlineStr">
@@ -30387,7 +31135,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J832" s="2" t="inlineStr"/>
+      <c r="J832" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" s="2" t="inlineStr">
@@ -30425,7 +31177,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J833" s="2" t="inlineStr"/>
+      <c r="J833" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="2" t="inlineStr">
@@ -30809,7 +31565,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J844" s="2" t="inlineStr"/>
+      <c r="J844" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" s="2" t="inlineStr">
@@ -30838,7 +31598,7 @@
       <c r="F845" s="2" t="inlineStr"/>
       <c r="G845" s="3" t="inlineStr">
         <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B — 1 шт.</t>
+          <t>Гидроблок вариатора — 1 шт.</t>
         </is>
       </c>
       <c r="H845" s="2" t="inlineStr"/>
@@ -30847,7 +31607,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J845" s="2" t="inlineStr"/>
+      <c r="J845" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" s="2" t="inlineStr">
@@ -30885,7 +31649,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J846" s="2" t="inlineStr"/>
+      <c r="J846" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" s="2" t="inlineStr">
@@ -30923,7 +31691,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J847" s="2" t="inlineStr"/>
+      <c r="J847" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" s="2" t="inlineStr">
@@ -34429,7 +35201,11 @@
           <t>артикул из названия</t>
         </is>
       </c>
-      <c r="J946" s="2" t="inlineStr"/>
+      <c r="J946" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="947">
       <c r="A947" s="2" t="inlineStr">
@@ -34503,7 +35279,11 @@
           <t>справочник Ozon</t>
         </is>
       </c>
-      <c r="J948" s="2" t="inlineStr"/>
+      <c r="J948" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="2" t="inlineStr">
@@ -34541,7 +35321,11 @@
           <t>из названия — проверьте</t>
         </is>
       </c>
-      <c r="J949" s="2" t="inlineStr"/>
+      <c r="J949" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="950">
       <c r="A950" s="2" t="inlineStr">
@@ -34579,7 +35363,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J950" s="2" t="inlineStr"/>
+      <c r="J950" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="951">
       <c r="A951" s="2" t="inlineStr">
@@ -34617,7 +35405,11 @@
           <t>одна деталь</t>
         </is>
       </c>
-      <c r="J951" s="2" t="inlineStr"/>
+      <c r="J951" s="2" t="inlineStr">
+        <is>
+          <t>ждёт</t>
+        </is>
+      </c>
     </row>
     <row r="952">
       <c r="A952" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10535,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -5731,7 +5731,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7397,7 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8921,7 +8921,7 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10535,7 +10535,7 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J343" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15437,7 +15437,7 @@
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -10903,7 +10903,7 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11541,7 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="J314" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="J324" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="J326" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="J340" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="J341" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="J342" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13179,7 +13179,7 @@
       </c>
       <c r="J343" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J354" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="J368" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="J382" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="J383" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14647,7 +14647,7 @@
       </c>
       <c r="J384" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="J385" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15077,7 +15077,7 @@
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15437,7 +15437,7 @@
       </c>
       <c r="J406" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15515,7 @@
       </c>
       <c r="J408" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="J409" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="J410" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16555,7 +16555,7 @@
       </c>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -18731,7 +18731,7 @@
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -19021,7 +19021,7 @@
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -20075,7 +20075,7 @@
       </c>
       <c r="J531" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="J532" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -20551,7 +20551,7 @@
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -15955,7 +15955,7 @@
       </c>
       <c r="J420" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16033,7 @@
       </c>
       <c r="J422" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="J423" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="J424" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="J434" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16555,7 +16555,7 @@
       </c>
       <c r="J436" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="J437" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="J438" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17011,7 +17011,7 @@
       </c>
       <c r="J448" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="J450" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17169,7 @@
       </c>
       <c r="J452" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="J466" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="J476" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18129,7 @@
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18171,7 +18171,7 @@
       </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="J490" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="J492" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="J493" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18731,7 +18731,7 @@
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19021,7 +19021,7 @@
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="J528" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="J530" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20075,7 +20075,7 @@
       </c>
       <c r="J531" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20117,7 +20117,7 @@
       </c>
       <c r="J532" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20551,7 +20551,7 @@
       </c>
       <c r="J544" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="J558" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="J559" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="J570" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="J572" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="J573" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -22135,7 +22135,7 @@
       </c>
       <c r="J587" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -22603,7 +22603,7 @@
       </c>
       <c r="J600" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="J612" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23113,7 +23113,7 @@
       </c>
       <c r="J614" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23155,7 +23155,7 @@
       </c>
       <c r="J615" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="J616" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23619,7 +23619,7 @@
       </c>
       <c r="J628" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="J629" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23703,7 +23703,7 @@
       </c>
       <c r="J630" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -23745,7 +23745,7 @@
       </c>
       <c r="J631" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24133,7 @@
       </c>
       <c r="J642" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24175,7 @@
       </c>
       <c r="J643" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="J644" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -24643,7 +24643,7 @@
       </c>
       <c r="J656" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="J657" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="J658" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25157,7 +25157,7 @@
       </c>
       <c r="J670" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="J671" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="J672" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="J680" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25569,7 @@
       </c>
       <c r="J681" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25611,7 +25611,7 @@
       </c>
       <c r="J682" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -25653,7 +25653,7 @@
       </c>
       <c r="J683" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -20975,7 +20975,7 @@
       </c>
       <c r="J556" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="J558" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21095,7 +21095,7 @@
       </c>
       <c r="J559" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21137,7 +21137,7 @@
       </c>
       <c r="J560" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21493,7 +21493,7 @@
       </c>
       <c r="J570" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21575,7 +21575,7 @@
       </c>
       <c r="J572" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="J573" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21659,7 +21659,7 @@
       </c>
       <c r="J574" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22015,7 +22015,7 @@
       </c>
       <c r="J584" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="J586" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22135,7 +22135,7 @@
       </c>
       <c r="J587" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="J588" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22603,7 +22603,7 @@
       </c>
       <c r="J600" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="J612" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23113,7 +23113,7 @@
       </c>
       <c r="J614" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23155,7 +23155,7 @@
       </c>
       <c r="J615" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="J616" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23619,7 +23619,7 @@
       </c>
       <c r="J628" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23661,7 +23661,7 @@
       </c>
       <c r="J629" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23703,7 +23703,7 @@
       </c>
       <c r="J630" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23745,7 +23745,7 @@
       </c>
       <c r="J631" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24133,7 @@
       </c>
       <c r="J642" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24175,7 @@
       </c>
       <c r="J643" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="J644" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24643,7 +24643,7 @@
       </c>
       <c r="J656" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="J657" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24727,7 +24727,7 @@
       </c>
       <c r="J658" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25157,7 +25157,7 @@
       </c>
       <c r="J670" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="J671" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="J672" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="J680" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25569,7 @@
       </c>
       <c r="J681" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25611,7 +25611,7 @@
       </c>
       <c r="J682" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25653,7 +25653,7 @@
       </c>
       <c r="J683" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26045,7 +26045,7 @@
       </c>
       <c r="J694" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="J695" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="J696" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="J706" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="J708" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26605,7 +26605,7 @@
       </c>
       <c r="J709" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26647,7 +26647,7 @@
       </c>
       <c r="J710" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26863,7 +26863,7 @@
       </c>
       <c r="J716" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="J718" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -26983,7 +26983,7 @@
       </c>
       <c r="J719" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27025,7 +27025,7 @@
       </c>
       <c r="J720" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27397,7 +27397,7 @@
       </c>
       <c r="J730" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27475,7 +27475,7 @@
       </c>
       <c r="J732" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="J733" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27559,7 +27559,7 @@
       </c>
       <c r="J734" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="J744" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="J746" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -28035,7 +28035,7 @@
       </c>
       <c r="J747" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="J748" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -28503,7 +28503,7 @@
       </c>
       <c r="J760" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="J761" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="J762" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="J774" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -29059,7 +29059,7 @@
       </c>
       <c r="J775" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="J776" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -30543,7 +30543,7 @@
       </c>
       <c r="J816" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="J817" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="J818" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="J819" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="J830" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31095,7 +31095,7 @@
       </c>
       <c r="J831" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31137,7 +31137,7 @@
       </c>
       <c r="J832" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31179,7 +31179,7 @@
       </c>
       <c r="J833" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31567,7 +31567,7 @@
       </c>
       <c r="J844" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31609,7 +31609,7 @@
       </c>
       <c r="J845" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31651,7 +31651,7 @@
       </c>
       <c r="J846" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -31693,7 +31693,7 @@
       </c>
       <c r="J847" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -26045,7 +26045,7 @@
       </c>
       <c r="J694" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="J695" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26129,7 +26129,7 @@
       </c>
       <c r="J696" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26485,7 +26485,7 @@
       </c>
       <c r="J706" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="J708" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26605,7 +26605,7 @@
       </c>
       <c r="J709" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26647,7 +26647,7 @@
       </c>
       <c r="J710" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26863,7 +26863,7 @@
       </c>
       <c r="J716" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="J718" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26983,7 +26983,7 @@
       </c>
       <c r="J719" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27025,7 +27025,7 @@
       </c>
       <c r="J720" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27397,7 +27397,7 @@
       </c>
       <c r="J730" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27475,7 +27475,7 @@
       </c>
       <c r="J732" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27517,7 +27517,7 @@
       </c>
       <c r="J733" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27559,7 +27559,7 @@
       </c>
       <c r="J734" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27915,7 +27915,7 @@
       </c>
       <c r="J744" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="J746" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28035,7 +28035,7 @@
       </c>
       <c r="J747" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28077,7 +28077,7 @@
       </c>
       <c r="J748" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28503,7 +28503,7 @@
       </c>
       <c r="J760" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28545,7 +28545,7 @@
       </c>
       <c r="J761" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="J762" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="J774" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -29059,7 +29059,7 @@
       </c>
       <c r="J775" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="J776" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30543,7 +30543,7 @@
       </c>
       <c r="J816" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="J817" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="J818" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="J819" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31053,7 +31053,7 @@
       </c>
       <c r="J830" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31095,7 +31095,7 @@
       </c>
       <c r="J831" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31137,7 +31137,7 @@
       </c>
       <c r="J832" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31179,7 +31179,7 @@
       </c>
       <c r="J833" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31567,7 +31567,7 @@
       </c>
       <c r="J844" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31609,7 +31609,7 @@
       </c>
       <c r="J845" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31651,7 +31651,7 @@
       </c>
       <c r="J846" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31693,7 +31693,7 @@
       </c>
       <c r="J847" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35203,7 +35203,7 @@
       </c>
       <c r="J946" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -35281,7 +35281,7 @@
       </c>
       <c r="J948" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="J949" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="J950" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -35407,7 +35407,7 @@
       </c>
       <c r="J951" s="2" t="inlineStr">
         <is>
-          <t>ждёт</t>
+          <t>да</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -35203,7 +35203,7 @@
       </c>
       <c r="J946" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35281,7 +35281,7 @@
       </c>
       <c r="J948" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="J949" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35365,7 +35365,7 @@
       </c>
       <c r="J950" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35407,7 +35407,7 @@
       </c>
       <c r="J951" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -806,14 +806,22 @@
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий, Пластик</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -840,14 +848,22 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>черный, серебристый</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1312,14 +1328,22 @@
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина, Алюминий</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1346,14 +1370,22 @@
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1846,14 +1878,22 @@
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий, Пластик</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1880,14 +1920,22 @@
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>черный, серебристый</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2372,14 +2420,22 @@
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Пластик, Металл</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2406,14 +2462,22 @@
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>серебристый, черный</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2894,14 +2958,22 @@
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3428,14 +3500,22 @@
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3462,14 +3542,22 @@
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3926,14 +4014,22 @@
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Металл, Пластик</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3960,14 +4056,22 @@
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4444,14 +4548,22 @@
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4478,14 +4590,22 @@
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4962,14 +5082,22 @@
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4996,14 +5124,22 @@
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5468,14 +5604,22 @@
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5502,14 +5646,22 @@
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6134,14 +6134,22 @@
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -6168,14 +6176,22 @@
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>черный, серый</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -6632,14 +6648,22 @@
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6666,14 +6690,22 @@
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>черный, серый</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="n"/>
       <c r="I164" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -7162,14 +7194,22 @@
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -7692,14 +7732,22 @@
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J191" s="2" t="inlineStr"/>
+      <c r="J191" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -7726,14 +7774,22 @@
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J192" s="2" t="inlineStr"/>
+      <c r="J192" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -8206,14 +8262,22 @@
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="n"/>
       <c r="I205" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J205" s="2" t="inlineStr"/>
+      <c r="J205" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -8240,14 +8304,22 @@
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>серебристый, зеленый</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="n"/>
       <c r="I206" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J206" s="2" t="inlineStr"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -8728,14 +8800,22 @@
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
-      <c r="H219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="n"/>
       <c r="I219" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J219" s="2" t="inlineStr"/>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -9258,14 +9338,22 @@
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr"/>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Металл, Пластик</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n"/>
       <c r="I233" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J233" s="2" t="inlineStr"/>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -9292,14 +9380,22 @@
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n"/>
       <c r="I234" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J234" s="2" t="inlineStr"/>
+      <c r="J234" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -9760,14 +9856,22 @@
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n"/>
       <c r="I247" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J247" s="2" t="inlineStr"/>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -9794,14 +9898,22 @@
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr"/>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>черный, зеленый</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n"/>
       <c r="I248" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr"/>
+      <c r="J248" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -10270,14 +10382,22 @@
         </is>
       </c>
       <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr"/>
-      <c r="H261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n"/>
       <c r="I261" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J261" s="2" t="inlineStr"/>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -10304,14 +10424,22 @@
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr"/>
-      <c r="H262" s="2" t="inlineStr"/>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>черный, зеленый</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="n"/>
       <c r="I262" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J262" s="2" t="inlineStr"/>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -10792,14 +10920,22 @@
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n"/>
       <c r="I275" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J275" s="2" t="inlineStr"/>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -10826,14 +10962,22 @@
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>черный, серебристый</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n"/>
       <c r="I276" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J276" s="2" t="inlineStr"/>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -2960,7 +2960,7 @@
       <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Алюминий</t>
+          <t>Металл</t>
         </is>
       </c>
       <c r="H65" s="2" t="n"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>отправлено 27.10</t>
+          <t>заменить</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11980,14 +11980,22 @@
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr"/>
-      <c r="G303" s="2" t="inlineStr"/>
-      <c r="H303" s="2" t="inlineStr"/>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="n"/>
       <c r="I303" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J303" s="2" t="inlineStr"/>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -12514,14 +12522,22 @@
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr"/>
-      <c r="H317" s="2" t="inlineStr"/>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="n"/>
       <c r="I317" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J317" s="2" t="inlineStr"/>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -12548,14 +12564,22 @@
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr"/>
-      <c r="H318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="n"/>
       <c r="I318" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J318" s="2" t="inlineStr"/>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -13016,14 +13040,22 @@
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr"/>
-      <c r="H331" s="2" t="inlineStr"/>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="n"/>
       <c r="I331" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J331" s="2" t="inlineStr"/>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -13050,14 +13082,22 @@
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
-      <c r="G332" s="2" t="inlineStr"/>
-      <c r="H332" s="2" t="inlineStr"/>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>черный, серый</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="n"/>
       <c r="I332" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J332" s="2" t="inlineStr"/>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -13542,14 +13582,22 @@
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
-      <c r="G345" s="2" t="inlineStr"/>
-      <c r="H345" s="2" t="inlineStr"/>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="n"/>
       <c r="I345" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J345" s="2" t="inlineStr"/>
+      <c r="J345" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -13576,14 +13624,22 @@
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr"/>
-      <c r="H346" s="2" t="inlineStr"/>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="n"/>
       <c r="I346" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J346" s="2" t="inlineStr"/>
+      <c r="J346" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -14044,14 +14100,22 @@
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
-      <c r="G359" s="2" t="inlineStr"/>
-      <c r="H359" s="2" t="inlineStr"/>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>Металл, Резина</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="n"/>
       <c r="I359" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J359" s="2" t="inlineStr"/>
+      <c r="J359" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -14538,14 +14602,22 @@
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr"/>
-      <c r="G373" s="2" t="inlineStr"/>
-      <c r="H373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина, Алюминий</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="n"/>
       <c r="I373" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J373" s="2" t="inlineStr"/>
+      <c r="J373" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -14572,14 +14644,22 @@
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr"/>
-      <c r="H374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>серебристый, черный, золотой</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="n"/>
       <c r="I374" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J374" s="2" t="inlineStr"/>
+      <c r="J374" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -15052,14 +15132,22 @@
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
-      <c r="G387" s="2" t="inlineStr"/>
-      <c r="H387" s="2" t="inlineStr"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="n"/>
       <c r="I387" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J387" s="2" t="inlineStr"/>
+      <c r="J387" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -15086,14 +15174,22 @@
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr"/>
-      <c r="G388" s="2" t="inlineStr"/>
-      <c r="H388" s="2" t="inlineStr"/>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="n"/>
       <c r="I388" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J388" s="2" t="inlineStr"/>
+      <c r="J388" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -15516,14 +15612,22 @@
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr"/>
-      <c r="G400" s="2" t="inlineStr"/>
-      <c r="H400" s="2" t="inlineStr"/>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Металл</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="n"/>
       <c r="I400" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J400" s="2" t="inlineStr"/>
+      <c r="J400" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -15550,14 +15654,22 @@
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr"/>
-      <c r="G401" s="2" t="inlineStr"/>
-      <c r="H401" s="2" t="inlineStr"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="n"/>
       <c r="I401" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J401" s="2" t="inlineStr"/>
+      <c r="J401" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -16000,14 +16112,22 @@
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr"/>
-      <c r="G413" s="2" t="inlineStr"/>
-      <c r="H413" s="2" t="inlineStr"/>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="n"/>
       <c r="I413" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J413" s="2" t="inlineStr"/>
+      <c r="J413" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -16034,14 +16154,22 @@
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr"/>
-      <c r="G414" s="2" t="inlineStr"/>
-      <c r="H414" s="2" t="inlineStr"/>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>золотой</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="n"/>
       <c r="I414" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J414" s="2" t="inlineStr"/>
+      <c r="J414" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>заменить</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13053,7 +13053,7 @@
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="J345" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="J359" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="J373" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="J374" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15145,7 +15145,7 @@
       </c>
       <c r="J387" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="J388" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15625,7 +15625,7 @@
       </c>
       <c r="J400" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="J401" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="J413" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="J414" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16646,14 +16646,22 @@
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr"/>
-      <c r="H427" s="2" t="inlineStr"/>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="n"/>
       <c r="I427" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J427" s="2" t="inlineStr"/>
+      <c r="J427" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -16680,14 +16688,22 @@
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr"/>
-      <c r="H428" s="2" t="inlineStr"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>зеленый</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="n"/>
       <c r="I428" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J428" s="2" t="inlineStr"/>
+      <c r="J428" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -17168,14 +17184,22 @@
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr"/>
-      <c r="H441" s="2" t="inlineStr"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="n"/>
       <c r="I441" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J441" s="2" t="inlineStr"/>
+      <c r="J441" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -18224,14 +18248,22 @@
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
-      <c r="G469" s="2" t="inlineStr"/>
-      <c r="H469" s="2" t="inlineStr"/>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="n"/>
       <c r="I469" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J469" s="2" t="inlineStr"/>
+      <c r="J469" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -18258,14 +18290,22 @@
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
-      <c r="G470" s="2" t="inlineStr"/>
-      <c r="H470" s="2" t="inlineStr"/>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="n"/>
       <c r="I470" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J470" s="2" t="inlineStr"/>
+      <c r="J470" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -18742,14 +18782,22 @@
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr"/>
-      <c r="G483" s="2" t="inlineStr"/>
-      <c r="H483" s="2" t="inlineStr"/>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>Металл, Резина</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="n"/>
       <c r="I483" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J483" s="2" t="inlineStr"/>
+      <c r="J483" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -18776,14 +18824,22 @@
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr"/>
-      <c r="H484" s="2" t="inlineStr"/>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="n"/>
       <c r="I484" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J484" s="2" t="inlineStr"/>
+      <c r="J484" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -19634,14 +19690,22 @@
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
-      <c r="G507" s="2" t="inlineStr"/>
-      <c r="H507" s="2" t="inlineStr"/>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>Металл</t>
+        </is>
+      </c>
+      <c r="H507" s="2" t="n"/>
       <c r="I507" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J507" s="2" t="inlineStr"/>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -19668,14 +19732,22 @@
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr"/>
-      <c r="G508" s="2" t="inlineStr"/>
-      <c r="H508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H508" s="2" t="n"/>
       <c r="I508" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J508" s="2" t="inlineStr"/>
+      <c r="J508" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -20128,14 +20200,22 @@
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr"/>
-      <c r="G521" s="2" t="inlineStr"/>
-      <c r="H521" s="2" t="inlineStr"/>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H521" s="2" t="n"/>
       <c r="I521" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J521" s="2" t="inlineStr"/>
+      <c r="J521" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -20162,14 +20242,22 @@
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr"/>
-      <c r="G522" s="2" t="inlineStr"/>
-      <c r="H522" s="2" t="inlineStr"/>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H522" s="2" t="n"/>
       <c r="I522" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J522" s="2" t="inlineStr"/>
+      <c r="J522" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -20646,14 +20734,22 @@
         </is>
       </c>
       <c r="F535" s="2" t="inlineStr"/>
-      <c r="G535" s="2" t="inlineStr"/>
-      <c r="H535" s="2" t="inlineStr"/>
+      <c r="G535" s="2" t="inlineStr">
+        <is>
+          <t>Металл</t>
+        </is>
+      </c>
+      <c r="H535" s="2" t="n"/>
       <c r="I535" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J535" s="2" t="inlineStr"/>
+      <c r="J535" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -20680,14 +20776,22 @@
         </is>
       </c>
       <c r="F536" s="2" t="inlineStr"/>
-      <c r="G536" s="2" t="inlineStr"/>
-      <c r="H536" s="2" t="inlineStr"/>
+      <c r="G536" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H536" s="2" t="n"/>
       <c r="I536" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J536" s="2" t="inlineStr"/>
+      <c r="J536" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -21148,14 +21252,22 @@
         </is>
       </c>
       <c r="F549" s="2" t="inlineStr"/>
-      <c r="G549" s="2" t="inlineStr"/>
-      <c r="H549" s="2" t="inlineStr"/>
+      <c r="G549" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H549" s="2" t="n"/>
       <c r="I549" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J549" s="2" t="inlineStr"/>
+      <c r="J549" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -21182,14 +21294,22 @@
         </is>
       </c>
       <c r="F550" s="2" t="inlineStr"/>
-      <c r="G550" s="2" t="inlineStr"/>
-      <c r="H550" s="2" t="inlineStr"/>
+      <c r="G550" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H550" s="2" t="n"/>
       <c r="I550" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J550" s="2" t="inlineStr"/>
+      <c r="J550" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -22188,14 +22308,22 @@
         </is>
       </c>
       <c r="F577" s="2" t="inlineStr"/>
-      <c r="G577" s="2" t="inlineStr"/>
-      <c r="H577" s="2" t="inlineStr"/>
+      <c r="G577" s="2" t="inlineStr">
+        <is>
+          <t>Бумага, Пластик</t>
+        </is>
+      </c>
+      <c r="H577" s="2" t="n"/>
       <c r="I577" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J577" s="2" t="inlineStr"/>
+      <c r="J577" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -22222,14 +22350,22 @@
         </is>
       </c>
       <c r="F578" s="2" t="inlineStr"/>
-      <c r="G578" s="2" t="inlineStr"/>
-      <c r="H578" s="2" t="inlineStr"/>
+      <c r="G578" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="H578" s="2" t="n"/>
       <c r="I578" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J578" s="2" t="inlineStr"/>
+      <c r="J578" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -22706,14 +22842,22 @@
         </is>
       </c>
       <c r="F591" s="2" t="inlineStr"/>
-      <c r="G591" s="2" t="inlineStr"/>
-      <c r="H591" s="2" t="inlineStr"/>
+      <c r="G591" s="2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="H591" s="2" t="n"/>
       <c r="I591" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J591" s="2" t="inlineStr"/>
+      <c r="J591" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -22740,14 +22884,22 @@
         </is>
       </c>
       <c r="F592" s="2" t="inlineStr"/>
-      <c r="G592" s="2" t="inlineStr"/>
-      <c r="H592" s="2" t="inlineStr"/>
+      <c r="G592" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H592" s="2" t="n"/>
       <c r="I592" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J592" s="2" t="inlineStr"/>
+      <c r="J592" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -16659,7 +16659,7 @@
       </c>
       <c r="J427" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="J428" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="J441" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18303,7 @@
       </c>
       <c r="J470" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18795,7 +18795,7 @@
       </c>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -18837,7 +18837,7 @@
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19703,7 +19703,7 @@
       </c>
       <c r="J507" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="J508" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20213,7 @@
       </c>
       <c r="J521" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20255,7 +20255,7 @@
       </c>
       <c r="J522" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20747,7 +20747,7 @@
       </c>
       <c r="J535" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -20789,7 +20789,7 @@
       </c>
       <c r="J536" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21265,7 +21265,7 @@
       </c>
       <c r="J549" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -21307,7 +21307,7 @@
       </c>
       <c r="J550" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22321,7 +22321,7 @@
       </c>
       <c r="J577" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22363,7 +22363,7 @@
       </c>
       <c r="J578" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22855,7 +22855,7 @@
       </c>
       <c r="J591" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -22897,7 +22897,7 @@
       </c>
       <c r="J592" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23348,14 +23348,22 @@
         </is>
       </c>
       <c r="F605" s="2" t="inlineStr"/>
-      <c r="G605" s="2" t="inlineStr"/>
-      <c r="H605" s="2" t="inlineStr"/>
+      <c r="G605" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H605" s="2" t="n"/>
       <c r="I605" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J605" s="2" t="inlineStr"/>
+      <c r="J605" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -23382,14 +23390,22 @@
         </is>
       </c>
       <c r="F606" s="2" t="inlineStr"/>
-      <c r="G606" s="2" t="inlineStr"/>
-      <c r="H606" s="2" t="inlineStr"/>
+      <c r="G606" s="2" t="inlineStr">
+        <is>
+          <t>серебристый, черный</t>
+        </is>
+      </c>
+      <c r="H606" s="2" t="n"/>
       <c r="I606" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -23874,14 +23890,22 @@
         </is>
       </c>
       <c r="F619" s="2" t="inlineStr"/>
-      <c r="G619" s="2" t="inlineStr"/>
-      <c r="H619" s="2" t="inlineStr"/>
+      <c r="G619" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H619" s="2" t="n"/>
       <c r="I619" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J619" s="2" t="inlineStr"/>
+      <c r="J619" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -23908,14 +23932,22 @@
         </is>
       </c>
       <c r="F620" s="2" t="inlineStr"/>
-      <c r="G620" s="2" t="inlineStr"/>
-      <c r="H620" s="2" t="inlineStr"/>
+      <c r="G620" s="2" t="inlineStr">
+        <is>
+          <t>зеленый</t>
+        </is>
+      </c>
+      <c r="H620" s="2" t="n"/>
       <c r="I620" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J620" s="2" t="inlineStr"/>
+      <c r="J620" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -24388,14 +24420,22 @@
         </is>
       </c>
       <c r="F633" s="2" t="inlineStr"/>
-      <c r="G633" s="2" t="inlineStr"/>
-      <c r="H633" s="2" t="inlineStr"/>
+      <c r="G633" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H633" s="2" t="n"/>
       <c r="I633" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J633" s="2" t="inlineStr"/>
+      <c r="J633" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -24422,14 +24462,22 @@
         </is>
       </c>
       <c r="F634" s="2" t="inlineStr"/>
-      <c r="G634" s="2" t="inlineStr"/>
-      <c r="H634" s="2" t="inlineStr"/>
+      <c r="G634" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H634" s="2" t="n"/>
       <c r="I634" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J634" s="2" t="inlineStr"/>
+      <c r="J634" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -24898,14 +24946,22 @@
         </is>
       </c>
       <c r="F647" s="2" t="inlineStr"/>
-      <c r="G647" s="2" t="inlineStr"/>
-      <c r="H647" s="2" t="inlineStr"/>
+      <c r="G647" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H647" s="2" t="n"/>
       <c r="I647" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J647" s="2" t="inlineStr"/>
+      <c r="J647" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -24932,14 +24988,22 @@
         </is>
       </c>
       <c r="F648" s="2" t="inlineStr"/>
-      <c r="G648" s="2" t="inlineStr"/>
-      <c r="H648" s="2" t="inlineStr"/>
+      <c r="G648" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H648" s="2" t="n"/>
       <c r="I648" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J648" s="2" t="inlineStr"/>
+      <c r="J648" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="2" t="inlineStr">
@@ -25404,14 +25468,22 @@
         </is>
       </c>
       <c r="F661" s="2" t="inlineStr"/>
-      <c r="G661" s="2" t="inlineStr"/>
-      <c r="H661" s="2" t="inlineStr"/>
+      <c r="G661" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H661" s="2" t="n"/>
       <c r="I661" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J661" s="2" t="inlineStr"/>
+      <c r="J661" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -25438,14 +25510,22 @@
         </is>
       </c>
       <c r="F662" s="2" t="inlineStr"/>
-      <c r="G662" s="2" t="inlineStr"/>
-      <c r="H662" s="2" t="inlineStr"/>
+      <c r="G662" s="2" t="inlineStr">
+        <is>
+          <t>золотой</t>
+        </is>
+      </c>
+      <c r="H662" s="2" t="n"/>
       <c r="I662" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J662" s="2" t="inlineStr"/>
+      <c r="J662" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
@@ -26296,14 +26376,22 @@
         </is>
       </c>
       <c r="F685" s="2" t="inlineStr"/>
-      <c r="G685" s="2" t="inlineStr"/>
-      <c r="H685" s="2" t="inlineStr"/>
+      <c r="G685" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H685" s="2" t="n"/>
       <c r="I685" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J685" s="2" t="inlineStr"/>
+      <c r="J685" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -26330,14 +26418,22 @@
         </is>
       </c>
       <c r="F686" s="2" t="inlineStr"/>
-      <c r="G686" s="2" t="inlineStr"/>
-      <c r="H686" s="2" t="inlineStr"/>
+      <c r="G686" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H686" s="2" t="n"/>
       <c r="I686" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J686" s="2" t="inlineStr"/>
+      <c r="J686" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -26810,14 +26906,22 @@
         </is>
       </c>
       <c r="F699" s="2" t="inlineStr"/>
-      <c r="G699" s="2" t="inlineStr"/>
-      <c r="H699" s="2" t="inlineStr"/>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>Бумага, Пластик</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="n"/>
       <c r="I699" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J699" s="2" t="inlineStr"/>
+      <c r="J699" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -26844,14 +26948,22 @@
         </is>
       </c>
       <c r="F700" s="2" t="inlineStr"/>
-      <c r="G700" s="2" t="inlineStr"/>
-      <c r="H700" s="2" t="inlineStr"/>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="n"/>
       <c r="I700" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J700" s="2" t="inlineStr"/>
+      <c r="J700" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -27290,14 +27402,22 @@
         </is>
       </c>
       <c r="F712" s="2" t="inlineStr"/>
-      <c r="G712" s="2" t="inlineStr"/>
-      <c r="H712" s="2" t="inlineStr"/>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>Пластик, Металл</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="n"/>
       <c r="I712" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J712" s="2" t="inlineStr"/>
+      <c r="J712" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" s="2" t="inlineStr">
@@ -28240,14 +28360,22 @@
         </is>
       </c>
       <c r="F737" s="2" t="inlineStr"/>
-      <c r="G737" s="2" t="inlineStr"/>
-      <c r="H737" s="2" t="inlineStr"/>
+      <c r="G737" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H737" s="2" t="n"/>
       <c r="I737" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J737" s="2" t="inlineStr"/>
+      <c r="J737" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" s="2" t="inlineStr">
@@ -28274,14 +28402,22 @@
         </is>
       </c>
       <c r="F738" s="2" t="inlineStr"/>
-      <c r="G738" s="2" t="inlineStr"/>
-      <c r="H738" s="2" t="inlineStr"/>
+      <c r="G738" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H738" s="2" t="n"/>
       <c r="I738" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J738" s="2" t="inlineStr"/>
+      <c r="J738" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="739">
       <c r="A739" s="2" t="inlineStr">
@@ -28758,14 +28894,22 @@
         </is>
       </c>
       <c r="F751" s="2" t="inlineStr"/>
-      <c r="G751" s="2" t="inlineStr"/>
-      <c r="H751" s="2" t="inlineStr"/>
+      <c r="G751" s="2" t="inlineStr">
+        <is>
+          <t>Бумага, Пластик</t>
+        </is>
+      </c>
+      <c r="H751" s="2" t="n"/>
       <c r="I751" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J751" s="2" t="inlineStr"/>
+      <c r="J751" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" s="2" t="inlineStr">
@@ -28792,14 +28936,22 @@
         </is>
       </c>
       <c r="F752" s="2" t="inlineStr"/>
-      <c r="G752" s="2" t="inlineStr"/>
-      <c r="H752" s="2" t="inlineStr"/>
+      <c r="G752" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="H752" s="2" t="n"/>
       <c r="I752" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J752" s="2" t="inlineStr"/>
+      <c r="J752" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -23361,7 +23361,7 @@
       </c>
       <c r="J605" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23403,7 +23403,7 @@
       </c>
       <c r="J606" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23903,7 +23903,7 @@
       </c>
       <c r="J619" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -23945,7 +23945,7 @@
       </c>
       <c r="J620" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="J633" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24475,7 +24475,7 @@
       </c>
       <c r="J634" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -24959,7 +24959,7 @@
       </c>
       <c r="J647" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="J648" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25481,7 +25481,7 @@
       </c>
       <c r="J661" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -25523,7 +25523,7 @@
       </c>
       <c r="J662" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26389,7 +26389,7 @@
       </c>
       <c r="J685" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="J686" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26919,7 +26919,7 @@
       </c>
       <c r="J699" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -26961,7 +26961,7 @@
       </c>
       <c r="J700" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="J712" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="J737" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28415,7 +28415,7 @@
       </c>
       <c r="J738" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28907,7 +28907,7 @@
       </c>
       <c r="J751" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -28949,7 +28949,7 @@
       </c>
       <c r="J752" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -29420,14 +29420,22 @@
         </is>
       </c>
       <c r="F765" s="2" t="inlineStr"/>
-      <c r="G765" s="2" t="inlineStr"/>
-      <c r="H765" s="2" t="inlineStr"/>
+      <c r="G765" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H765" s="2" t="n"/>
       <c r="I765" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J765" s="2" t="inlineStr"/>
+      <c r="J765" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="766">
       <c r="A766" s="2" t="inlineStr">
@@ -29454,14 +29462,22 @@
         </is>
       </c>
       <c r="F766" s="2" t="inlineStr"/>
-      <c r="G766" s="2" t="inlineStr"/>
-      <c r="H766" s="2" t="inlineStr"/>
+      <c r="G766" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H766" s="2" t="n"/>
       <c r="I766" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J766" s="2" t="inlineStr"/>
+      <c r="J766" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="767">
       <c r="A767" s="2" t="inlineStr">
@@ -29934,14 +29950,22 @@
         </is>
       </c>
       <c r="F779" s="2" t="inlineStr"/>
-      <c r="G779" s="2" t="inlineStr"/>
-      <c r="H779" s="2" t="inlineStr"/>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="n"/>
       <c r="I779" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J779" s="2" t="inlineStr"/>
+      <c r="J779" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" s="2" t="inlineStr">
@@ -29972,14 +29996,22 @@
           <t>серебристый</t>
         </is>
       </c>
-      <c r="G780" s="2" t="inlineStr"/>
-      <c r="H780" s="2" t="inlineStr"/>
+      <c r="G780" s="2" t="inlineStr">
+        <is>
+          <t>черный, зеленый</t>
+        </is>
+      </c>
+      <c r="H780" s="2" t="n"/>
       <c r="I780" s="2" t="inlineStr">
         <is>
           <t>уже заполнено — не трогаем</t>
         </is>
       </c>
-      <c r="J780" s="2" t="inlineStr"/>
+      <c r="J780" s="2" t="inlineStr">
+        <is>
+          <t>заменить</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" s="2" t="inlineStr">
@@ -30450,14 +30482,22 @@
         </is>
       </c>
       <c r="F793" s="2" t="inlineStr"/>
-      <c r="G793" s="2" t="inlineStr"/>
-      <c r="H793" s="2" t="inlineStr"/>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>Бумага, Резина</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="n"/>
       <c r="I793" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J793" s="2" t="inlineStr"/>
+      <c r="J793" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="794">
       <c r="A794" s="2" t="inlineStr">
@@ -30484,14 +30524,22 @@
         </is>
       </c>
       <c r="F794" s="2" t="inlineStr"/>
-      <c r="G794" s="2" t="inlineStr"/>
-      <c r="H794" s="2" t="inlineStr"/>
+      <c r="G794" s="2" t="inlineStr">
+        <is>
+          <t>белый</t>
+        </is>
+      </c>
+      <c r="H794" s="2" t="n"/>
       <c r="I794" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J794" s="2" t="inlineStr"/>
+      <c r="J794" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" s="2" t="inlineStr">
@@ -31460,14 +31508,22 @@
         </is>
       </c>
       <c r="F821" s="2" t="inlineStr"/>
-      <c r="G821" s="2" t="inlineStr"/>
-      <c r="H821" s="2" t="inlineStr"/>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="n"/>
       <c r="I821" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J821" s="2" t="inlineStr"/>
+      <c r="J821" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="822">
       <c r="A822" s="2" t="inlineStr">
@@ -31494,14 +31550,22 @@
         </is>
       </c>
       <c r="F822" s="2" t="inlineStr"/>
-      <c r="G822" s="2" t="inlineStr"/>
-      <c r="H822" s="2" t="inlineStr"/>
+      <c r="G822" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H822" s="2" t="n"/>
       <c r="I822" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J822" s="2" t="inlineStr"/>
+      <c r="J822" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" s="2" t="inlineStr">
@@ -31974,14 +32038,22 @@
         </is>
       </c>
       <c r="F835" s="2" t="inlineStr"/>
-      <c r="G835" s="2" t="inlineStr"/>
-      <c r="H835" s="2" t="inlineStr"/>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="n"/>
       <c r="I835" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J835" s="2" t="inlineStr"/>
+      <c r="J835" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" s="2" t="inlineStr">
@@ -32008,14 +32080,22 @@
         </is>
       </c>
       <c r="F836" s="2" t="inlineStr"/>
-      <c r="G836" s="2" t="inlineStr"/>
-      <c r="H836" s="2" t="inlineStr"/>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="n"/>
       <c r="I836" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J836" s="2" t="inlineStr"/>
+      <c r="J836" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="837">
       <c r="A837" s="2" t="inlineStr">
@@ -32488,14 +32568,22 @@
         </is>
       </c>
       <c r="F849" s="2" t="inlineStr"/>
-      <c r="G849" s="2" t="inlineStr"/>
-      <c r="H849" s="2" t="inlineStr"/>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="n"/>
       <c r="I849" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J849" s="2" t="inlineStr"/>
+      <c r="J849" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="850">
       <c r="A850" s="2" t="inlineStr">
@@ -32522,14 +32610,22 @@
         </is>
       </c>
       <c r="F850" s="2" t="inlineStr"/>
-      <c r="G850" s="2" t="inlineStr"/>
-      <c r="H850" s="2" t="inlineStr"/>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>серебристый</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="n"/>
       <c r="I850" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J850" s="2" t="inlineStr"/>
+      <c r="J850" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" s="2" t="inlineStr">
@@ -32810,14 +32906,22 @@
         </is>
       </c>
       <c r="F858" s="2" t="inlineStr"/>
-      <c r="G858" s="2" t="inlineStr"/>
-      <c r="H858" s="2" t="inlineStr"/>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>Пластик, Металл</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="n"/>
       <c r="I858" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J858" s="2" t="inlineStr"/>
+      <c r="J858" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" s="2" t="inlineStr">
@@ -33200,14 +33304,22 @@
         </is>
       </c>
       <c r="F869" s="2" t="inlineStr"/>
-      <c r="G869" s="2" t="inlineStr"/>
-      <c r="H869" s="2" t="inlineStr"/>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="n"/>
       <c r="I869" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J869" s="2" t="inlineStr"/>
+      <c r="J869" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" s="2" t="inlineStr">
@@ -33234,14 +33346,22 @@
         </is>
       </c>
       <c r="F870" s="2" t="inlineStr"/>
-      <c r="G870" s="2" t="inlineStr"/>
-      <c r="H870" s="2" t="inlineStr"/>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>бирюзовый</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="n"/>
       <c r="I870" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J870" s="2" t="inlineStr"/>
+      <c r="J870" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" s="2" t="inlineStr">
@@ -33692,14 +33812,22 @@
         </is>
       </c>
       <c r="F883" s="2" t="inlineStr"/>
-      <c r="G883" s="2" t="inlineStr"/>
-      <c r="H883" s="2" t="inlineStr"/>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="n"/>
       <c r="I883" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J883" s="2" t="inlineStr"/>
+      <c r="J883" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" s="2" t="inlineStr">
@@ -33726,14 +33854,22 @@
         </is>
       </c>
       <c r="F884" s="2" t="inlineStr"/>
-      <c r="G884" s="2" t="inlineStr"/>
-      <c r="H884" s="2" t="inlineStr"/>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>зеленый</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="n"/>
       <c r="I884" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J884" s="2" t="inlineStr"/>
+      <c r="J884" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" s="2" t="inlineStr">
@@ -34184,14 +34320,22 @@
         </is>
       </c>
       <c r="F897" s="2" t="inlineStr"/>
-      <c r="G897" s="2" t="inlineStr"/>
-      <c r="H897" s="2" t="inlineStr"/>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="n"/>
       <c r="I897" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J897" s="2" t="inlineStr"/>
+      <c r="J897" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="898">
       <c r="A898" s="2" t="inlineStr">
@@ -34218,14 +34362,22 @@
         </is>
       </c>
       <c r="F898" s="2" t="inlineStr"/>
-      <c r="G898" s="2" t="inlineStr"/>
-      <c r="H898" s="2" t="inlineStr"/>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>бирюзовый</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="n"/>
       <c r="I898" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J898" s="2" t="inlineStr"/>
+      <c r="J898" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="899">
       <c r="A899" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -29433,7 +29433,7 @@
       </c>
       <c r="J765" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="J766" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -29963,7 +29963,7 @@
       </c>
       <c r="J779" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30009,7 +30009,7 @@
       </c>
       <c r="J780" s="2" t="inlineStr">
         <is>
-          <t>заменить</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30495,7 +30495,7 @@
       </c>
       <c r="J793" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -30537,7 +30537,7 @@
       </c>
       <c r="J794" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31521,7 +31521,7 @@
       </c>
       <c r="J821" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="J822" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -32051,7 +32051,7 @@
       </c>
       <c r="J835" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -32093,7 +32093,7 @@
       </c>
       <c r="J836" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -32581,7 +32581,7 @@
       </c>
       <c r="J849" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="J850" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -32919,7 +32919,7 @@
       </c>
       <c r="J858" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -33317,7 +33317,7 @@
       </c>
       <c r="J869" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -33359,7 +33359,7 @@
       </c>
       <c r="J870" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -33825,7 +33825,7 @@
       </c>
       <c r="J883" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="J884" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -34333,7 +34333,7 @@
       </c>
       <c r="J897" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -34375,7 +34375,7 @@
       </c>
       <c r="J898" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -34836,14 +34836,22 @@
         </is>
       </c>
       <c r="F911" s="2" t="inlineStr"/>
-      <c r="G911" s="2" t="inlineStr"/>
-      <c r="H911" s="2" t="inlineStr"/>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>Пластик</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="n"/>
       <c r="I911" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J911" s="2" t="inlineStr"/>
+      <c r="J911" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
@@ -34870,14 +34878,22 @@
         </is>
       </c>
       <c r="F912" s="2" t="inlineStr"/>
-      <c r="G912" s="2" t="inlineStr"/>
-      <c r="H912" s="2" t="inlineStr"/>
+      <c r="G912" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="n"/>
       <c r="I912" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J912" s="2" t="inlineStr"/>
+      <c r="J912" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
@@ -35332,14 +35348,22 @@
         </is>
       </c>
       <c r="F925" s="2" t="inlineStr"/>
-      <c r="G925" s="2" t="inlineStr"/>
-      <c r="H925" s="2" t="inlineStr"/>
+      <c r="G925" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="n"/>
       <c r="I925" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J925" s="2" t="inlineStr"/>
+      <c r="J925" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
@@ -35366,14 +35390,22 @@
         </is>
       </c>
       <c r="F926" s="2" t="inlineStr"/>
-      <c r="G926" s="2" t="inlineStr"/>
-      <c r="H926" s="2" t="inlineStr"/>
+      <c r="G926" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H926" s="2" t="n"/>
       <c r="I926" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J926" s="2" t="inlineStr"/>
+      <c r="J926" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="927">
       <c r="A927" s="2" t="inlineStr">
@@ -35832,14 +35864,22 @@
         </is>
       </c>
       <c r="F939" s="2" t="inlineStr"/>
-      <c r="G939" s="2" t="inlineStr"/>
-      <c r="H939" s="2" t="inlineStr"/>
+      <c r="G939" s="2" t="inlineStr">
+        <is>
+          <t>Сталь, Резина</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="n"/>
       <c r="I939" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J939" s="2" t="inlineStr"/>
+      <c r="J939" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
@@ -35866,14 +35906,22 @@
         </is>
       </c>
       <c r="F940" s="2" t="inlineStr"/>
-      <c r="G940" s="2" t="inlineStr"/>
-      <c r="H940" s="2" t="inlineStr"/>
+      <c r="G940" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="n"/>
       <c r="I940" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J940" s="2" t="inlineStr"/>
+      <c r="J940" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
@@ -36354,14 +36402,22 @@
         </is>
       </c>
       <c r="F953" s="2" t="inlineStr"/>
-      <c r="G953" s="2" t="inlineStr"/>
-      <c r="H953" s="2" t="inlineStr"/>
+      <c r="G953" s="2" t="inlineStr">
+        <is>
+          <t>Алюминий, Пластик</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="n"/>
       <c r="I953" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J953" s="2" t="inlineStr"/>
+      <c r="J953" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" s="2" t="inlineStr">
@@ -36388,14 +36444,22 @@
         </is>
       </c>
       <c r="F954" s="2" t="inlineStr"/>
-      <c r="G954" s="2" t="inlineStr"/>
-      <c r="H954" s="2" t="inlineStr"/>
+      <c r="G954" s="2" t="inlineStr">
+        <is>
+          <t>серебристый, черный</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="n"/>
       <c r="I954" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J954" s="2" t="inlineStr"/>
+      <c r="J954" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="955">
       <c r="A955" s="2" t="inlineStr">
@@ -36850,14 +36914,22 @@
         </is>
       </c>
       <c r="F967" s="2" t="inlineStr"/>
-      <c r="G967" s="2" t="inlineStr"/>
-      <c r="H967" s="2" t="inlineStr"/>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>Резина</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="n"/>
       <c r="I967" s="2" t="inlineStr">
         <is>
           <t>выберите: ABS пластик [61704]; EVA [61716]; Taffeta [61737]; Акрил [61748]; Алюминий [61753]; Атлас [61756]; Бархат [61764]; Брезент [61772]; Бронза [61773]; Бумага [61776]; Вельвет [61780]; Велюр натуральный [61781]; Винил [61783]; Вискоза [61786]; Войлок [61791]; Высокоуглеродистая сталь [61799]; Габардин [61801]; Гелевый наполнитель [61802]; Гематит [61804]; Графит [61810]; Дерево [61815]; ДСП [61820]; Жаккард [61824]; Железо [61826]; Жесть [61828]</t>
         </is>
       </c>
-      <c r="J967" s="2" t="inlineStr"/>
+      <c r="J967" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="968">
       <c r="A968" s="2" t="inlineStr">
@@ -36884,14 +36956,22 @@
         </is>
       </c>
       <c r="F968" s="2" t="inlineStr"/>
-      <c r="G968" s="2" t="inlineStr"/>
-      <c r="H968" s="2" t="inlineStr"/>
+      <c r="G968" s="2" t="inlineStr">
+        <is>
+          <t>черный</t>
+        </is>
+      </c>
+      <c r="H968" s="2" t="n"/>
       <c r="I968" s="2" t="inlineStr">
         <is>
           <t>выберите: белый [61571]; прозрачный [61572]; бежевый [61573]; черный [61574]; коричневый [61575]; серый [61576]; серый металлик [61577]; желтый [61578]; красный [61579]; розовый [61580]; синий [61581]; золотой [61582]; зеленый [61583]; голубой [61584]; оранжевый [61585]; фиолетовый [61586]; бронза [61587]; сиреневый [61588]; светло-зеленый [61589]; бордовый [61590]; светло-коричневый [61591]; темно-синий [61592]; светло-бежевый [61593]; светло-серый [61594]; бирюзовый [61595]</t>
         </is>
       </c>
-      <c r="J968" s="2" t="inlineStr"/>
+      <c r="J968" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="969">
       <c r="A969" s="2" t="inlineStr">

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J973"/>
+  <dimension ref="A1:J975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -34849,7 +34849,7 @@
       </c>
       <c r="J911" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -34891,7 +34891,7 @@
       </c>
       <c r="J912" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35361,7 +35361,7 @@
       </c>
       <c r="J925" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35403,7 +35403,7 @@
       </c>
       <c r="J926" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35877,7 +35877,7 @@
       </c>
       <c r="J939" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -35919,7 +35919,7 @@
       </c>
       <c r="J940" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -36415,7 +36415,7 @@
       </c>
       <c r="J953" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -36457,7 +36457,7 @@
       </c>
       <c r="J954" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -36927,7 +36927,7 @@
       </c>
       <c r="J967" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -36969,7 +36969,7 @@
       </c>
       <c r="J968" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -37143,6 +37143,86 @@
       </c>
       <c r="J973" s="2" t="inlineStr"/>
     </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>02e305045</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Rich-контент JSON</t>
+        </is>
+      </c>
+      <c r="D974" t="n">
+        <v>11254</v>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://ir-20.ozone.ru/s3/multimedia-1-1/14848097509.jpg", "srcMobile": "https://ir-20.ozone.ru/s3/multimedia-1-1/14848097509.jpg", "alt": "Алюминиевый корпус масляного фильтра DSG6 DQ250 02E305045", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1200, "heightMobile": 1600, "isParandjaMobile": false}, "title": {"content": ["Алюминиевый корпус фильтра DSG6 DQ250 02E305045"], "size": "size4", "align": "left", "color": "color1"}, "text": {"content": ["Заменяет штатный пластиковый корпус на коробках DSG6 02E. Не трескается и не деформируется от нагрева, лучше отводит тепло от масла КПП. Резиновое уплотнительное кольцо в комплекте."], "size": "size2", "align": "left", "color": "color1"}}]}, {"widgetName": "raTextBlock", "title": {"content": ["✅ Совместимость"], "size": "size4", "align": "left", "color": "color1"}, "theme": "default", "padding": "type2", "gapSize": "m", "text": {"content": ["Коробки DSG6 02E (DQ250, мокрое сцепление)", "Volkswagen, Audi, Skoda, Seat"], "size": "size2", "align": "left", "color": "color1"}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://ir-20.ozone.ru/s3/multimedia-1-c/14848097268.jpg", "srcMobile": "https://ir-20.ozone.ru/s3/multimedia-1-c/14848097268.jpg", "alt": "Корпус фильтра DQ250 с уплотнительным кольцом", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1200, "heightMobile": 1600, "isParandjaMobile": false}, "title": {"content": ["📌 Когда устанавливать"], "size": "size4", "align": "left", "color": "color1"}, "text": {"content": ["Трещины или деформация штатного пластикового корпуса", "При регулярной замене фильтра — алюминиевый корпус служит многократно", "Если масло в коробке перегревается"], "size": "size2", "align": "left", "color": "color1"}}]}], "version": 0.3}</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>тест rich-контента (Claude)</t>
+        </is>
+      </c>
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>0BH325183</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Rich-контент JSON</t>
+        </is>
+      </c>
+      <c r="D975" t="n">
+        <v>11254</v>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>{"content": [{"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://ir-20.ozone.ru/s3/multimedia-1-l/14848103937.jpg", "srcMobile": "https://ir-20.ozone.ru/s3/multimedia-1-l/14848103937.jpg", "alt": "Ребристый алюминиевый корпус фильтра DSG7 DQ500 0BH325183B", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1200, "heightMobile": 1600, "isParandjaMobile": false}, "title": {"content": ["Алюминиевый ребристый корпус фильтра DSG7 DQ500 0BH325183B"], "size": "size4", "align": "left", "color": "color1"}, "text": {"content": ["Прочная замена пластиковому корпусу масляного фильтра коробок DQ500 (0BH, 0BT). Рёбра улучшают отвод тепла и снижают рабочую температуру масла. Уплотнительное кольцо в комплекте."], "size": "size2", "align": "left", "color": "color1"}}]}, {"widgetName": "raTextBlock", "title": {"content": ["🚗 Совместимость"], "size": "size4", "align": "left", "color": "color1"}, "theme": "default", "padding": "type2", "gapSize": "m", "text": {"content": ["Audi RS3, TTRS, Q3, Q5 с DSG7 DQ500", "Volkswagen Tiguan, Transporter T5/T6, Amarok с DSG7 DQ500", "Seat, Skoda с коробкой DQ500 (по каталогу)"], "size": "size2", "align": "left", "color": "color1"}}, {"widgetName": "raShowcase", "type": "roll", "blocks": [{"imgLink": "", "img": {"src": "https://ir-20.ozone.ru/s3/multimedia-1-y/14848100134.jpg", "srcMobile": "https://ir-20.ozone.ru/s3/multimedia-1-y/14848100134.jpg", "alt": "Корпус фильтра DQ500 с уплотнительным кольцом", "position": "width_full", "positionMobile": "width_full", "widthMobile": 1200, "heightMobile": 1600, "isParandjaMobile": false}, "title": {"content": ["🔥 Преимущества"], "size": "size4", "align": "left", "color": "color1"}, "text": {"content": ["Алюминиевый сплав — не трескается от перепадов температур", "Герметичная установка без протечек", "Многократное использование при плановом обслуживании"], "size": "size2", "align": "left", "color": "color1"}}]}], "version": 0.3}</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>тест rich-контента (Claude)</t>
+        </is>
+      </c>
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ozon_attr_plan.xlsx
+++ b/data/ozon_attr_plan.xlsx
@@ -37179,7 +37179,7 @@
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
@@ -37219,7 +37219,7 @@
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>отправлено 27.10</t>
         </is>
       </c>
     </row>
